--- a/INSTANCES/instances_xlsx/A_MTN_8/379FL_15A_1.xlsx
+++ b/INSTANCES/instances_xlsx/A_MTN_8/379FL_15A_1.xlsx
@@ -12037,7 +12037,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -12071,7 +12071,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -12105,7 +12105,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -12122,7 +12122,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -12224,7 +12224,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -12241,7 +12241,7 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -12258,7 +12258,7 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16">
         <v>1</v>
